--- a/tools/xlsform_samples/ONS-SWB4.xlsx
+++ b/tools/xlsform_samples/ONS-SWB4.xlsx
@@ -442,11 +442,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="58" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -702,84 +702,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ONS_SWB4_scoring</t>
+          <t>ONS_SWB4_swb</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Computed Scores</t>
+          <t>swb (sum_coded)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>${satisfaction} + ${worth} + ${happiness} + ${anxiety}</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ONS_SWB4_swb</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>swb (sum_coded)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>${satisfaction} + ${worth} + ${happiness} + ${anxiety}</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ONS_SWB4_scoring</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/xlsform_samples/ONS-SWB4.xlsx
+++ b/tools/xlsform_samples/ONS-SWB4.xlsx
@@ -823,7 +823,11 @@
           <t>20260618</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>English (en)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
